--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T09:05:22+00:00</t>
+    <t>2024-04-25T09:06:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-16T08:04:49+00:00</t>
+    <t>2024-05-23T12:00:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:00:22+00:00</t>
+    <t>2024-06-05T13:15:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:15:20+00:00</t>
+    <t>2024-06-05T13:17:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T13:17:40+00:00</t>
+    <t>2024-06-17T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-17T15:07:22+00:00</t>
+    <t>2024-07-01T14:59:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T13:41:42+00:00</t>
+    <t>2025-02-27T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T09:48:09+00:00</t>
+    <t>2025-03-04T08:17:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T08:17:54+00:00</t>
+    <t>2025-03-06T14:47:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:47:34+00:00</t>
+    <t>2025-03-07T13:06:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-07T13:06:03+00:00</t>
+    <t>2025-04-23T14:15:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2441,17 +2441,17 @@
   <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="52.88671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.3046875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="27.03125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.26953125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="23.171875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="223.14453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2460,28 +2460,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="98.61328125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="98.171875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="41.01953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="84.1640625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="247.40625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="107.01953125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="42.34375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.3046875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T14:15:06+00:00</t>
+    <t>2025-05-21T14:32:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-02T12:26:16+00:00</t>
+    <t>2025-07-21T12:31:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-21T12:31:31+00:00</t>
+    <t>2025-10-13T07:29:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -5368,7 +5368,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
         <v>243</v>
       </c>
@@ -5608,7 +5608,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>266</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
         <v>272</v>
       </c>
@@ -6330,7 +6330,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>285</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
         <v>303</v>
       </c>
@@ -7056,7 +7056,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
         <v>339</v>
       </c>
@@ -8624,7 +8624,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
         <v>376</v>
       </c>
@@ -8988,7 +8988,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
         <v>403</v>
       </c>
@@ -9470,7 +9470,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
         <v>444</v>
       </c>
@@ -9832,7 +9832,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
         <v>451</v>
       </c>
@@ -10076,7 +10076,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
         <v>472</v>
       </c>
@@ -10196,7 +10196,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
         <v>480</v>
       </c>
@@ -10316,7 +10316,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
         <v>489</v>
       </c>
@@ -10438,7 +10438,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>499</v>
       </c>
@@ -12246,7 +12246,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
         <v>548</v>
       </c>
@@ -12486,7 +12486,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
         <v>565</v>
       </c>
@@ -14046,7 +14046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
         <v>640</v>
       </c>
@@ -14528,7 +14528,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
         <v>650</v>
       </c>
@@ -14650,7 +14650,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="102" hidden="true">
+    <row r="102">
       <c r="A102" t="s" s="2">
         <v>656</v>
       </c>
@@ -14772,7 +14772,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="103" hidden="true">
+    <row r="103">
       <c r="A103" t="s" s="2">
         <v>665</v>
       </c>
@@ -15140,12 +15140,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP105">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="680">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:09+00:00</t>
+    <t>2025-10-13T07:29:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,7 +439,7 @@
 </t>
   </si>
   <si>
-    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’un oid : « urn:oid:xx.xx.xx »</t>
+    <t>Uri identifiant les systèmes tiers ayant envoyé la ressource. L’uri est sous la forme d’une oid : « urn:oid:xx.xx.xx »</t>
   </si>
   <si>
     <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
@@ -656,7 +656,7 @@
     <t>Other information that may be relevant to this event.</t>
   </si>
   <si>
-    <t>Other resources *from the patient record* that may be relevant to the event.  The information from these resources was either used to create the instance or is provided to help with its interpretation.  This extension **should not** be used if more specific  inline elements  or extensions are available.  For example, use `Observation.hasMember`  instead of supportingInformation for  representing the members of an Observation panel.</t>
+    <t>Autres ressources pertinentes *du dossier patient*</t>
   </si>
   <si>
     <t>Observation.extension:MesReasonForMeasurement</t>
@@ -672,7 +672,24 @@
     <t>Motif de la mesure</t>
   </si>
   <si>
-    <t>Extension du Motif de la mesure, exprimé en texte libre  (ex. diabète, surpoids, maladie du cœur et des vaisseaux, cholestérol…).</t>
+    <t>Motif de la mesure
+Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
+  </si>
+  <si>
+    <t>Observation.extension:MesOriginOfData</t>
+  </si>
+  <si>
+    <t>MesOriginOfData</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
+</t>
+  </si>
+  <si>
+    <t>Origine de la donnée</t>
+  </si>
+  <si>
+    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
   </si>
   <si>
     <t>Observation.modifierExtension</t>
@@ -1333,7 +1350,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2438,7 +2455,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP105"/>
+  <dimension ref="A1:AP106"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
@@ -2451,7 +2468,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="191.30859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4891,43 +4908,41 @@
         <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="C21" s="2"/>
+        <v>197</v>
+      </c>
+      <c r="C21" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="D21" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>114</v>
+        <v>213</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N21" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O21" t="s" s="2">
-        <v>214</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4975,7 +4990,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4999,7 +5014,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5017,7 +5032,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5030,23 +5045,25 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>217</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>218</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="N22" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="N22" s="2"/>
-      <c r="O22" t="s" s="2">
-        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5095,7 +5112,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5107,22 +5124,22 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>221</v>
+        <v>82</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>222</v>
+        <v>82</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>223</v>
+        <v>196</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>224</v>
+        <v>82</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5130,14 +5147,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>226</v>
+        <v>82</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5156,17 +5173,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5215,7 +5232,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5230,19 +5247,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>82</v>
+        <v>229</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5250,14 +5267,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5276,18 +5293,18 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O24" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5335,7 +5352,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5350,16 +5367,16 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5368,48 +5385,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="M25" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>247</v>
-      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5433,11 +5448,13 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y25" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z25" t="s" s="2">
-        <v>249</v>
+        <v>82</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5455,13 +5472,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5470,30 +5487,30 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>251</v>
+        <v>82</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>254</v>
+        <v>82</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5504,31 +5521,31 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5553,35 +5570,35 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>177</v>
-      </c>
-      <c r="Y26" t="s" s="2">
-        <v>261</v>
-      </c>
+        <v>253</v>
+      </c>
+      <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="AC26" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5590,34 +5607,32 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>82</v>
+        <v>255</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>82</v>
+        <v>256</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>82</v>
+        <v>257</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>267</v>
-      </c>
+        <v>260</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5626,7 +5641,7 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
@@ -5638,19 +5653,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5678,28 +5693,26 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>268</v>
+      </c>
+      <c r="AC27" s="2"/>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5723,35 +5736,37 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>260</v>
+      </c>
+      <c r="C28" t="s" s="2">
+        <v>272</v>
+      </c>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5760,16 +5775,20 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>108</v>
+        <v>262</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
+        <v>263</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5793,13 +5812,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>82</v>
+        <v>266</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>82</v>
+        <v>267</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5817,19 +5836,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>110</v>
+        <v>260</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5841,10 +5860,10 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>111</v>
+        <v>269</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>82</v>
+        <v>270</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5852,21 +5871,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5878,17 +5897,15 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5925,31 +5942,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5970,48 +5987,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6047,19 +6062,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6071,7 +6086,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6080,10 +6095,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6092,12 +6107,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31" hidden="true">
+    <row r="31">
       <c r="A31" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6105,31 +6120,35 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N31" s="2"/>
-      <c r="O31" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O31" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6177,19 +6196,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6198,10 +6217,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6212,21 +6231,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6238,17 +6257,15 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N32" s="2"/>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6285,31 +6302,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6330,134 +6347,132 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN33" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AO33" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP33" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>291</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="AG33" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH33" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="AI33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ33" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP33" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" hidden="true">
-      <c r="A34" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6465,13 +6480,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6480,24 +6495,26 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O34" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>82</v>
+        <v>296</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6539,7 +6556,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6560,24 +6577,24 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AN34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AO34" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="B35" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6585,13 +6602,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6600,24 +6617,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>308</v>
+        <v>82</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6659,7 +6676,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6680,10 +6697,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6692,12 +6709,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6705,13 +6722,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6720,24 +6737,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6779,7 +6796,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6800,10 +6817,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6814,10 +6831,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6840,19 +6857,17 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6901,7 +6916,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6922,10 +6937,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6936,10 +6951,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6962,19 +6977,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7023,7 +7038,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7044,10 +7059,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7056,26 +7071,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>340</v>
+        <v>82</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7084,19 +7099,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7121,13 +7136,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7145,10 +7160,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7160,62 +7175,66 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>347</v>
+        <v>82</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>348</v>
+        <v>82</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>346</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="O40" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7239,13 +7258,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>82</v>
+        <v>350</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7263,10 +7282,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>110</v>
+        <v>344</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7275,44 +7294,44 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>82</v>
+        <v>353</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>82</v>
+        <v>354</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>111</v>
+        <v>355</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>82</v>
+        <v>357</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7324,17 +7343,15 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7371,31 +7388,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7418,18 +7435,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>81</v>
@@ -7441,23 +7458,21 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7493,9 +7508,11 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC42" s="2"/>
+        <v>118</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7503,7 +7520,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7515,7 +7532,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7524,10 +7541,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7538,14 +7555,12 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>358</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7554,7 +7569,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7569,16 +7584,16 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7615,19 +7630,17 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC43" s="2"/>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7648,10 +7661,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7662,18 +7675,20 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="C44" s="2"/>
+      <c r="C44" t="s" s="2">
+        <v>363</v>
+      </c>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
@@ -7685,19 +7700,23 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7745,19 +7764,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7766,10 +7785,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7780,21 +7799,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7806,17 +7825,15 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7853,31 +7870,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7900,21 +7917,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7923,29 +7940,27 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>365</v>
+        <v>82</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7975,31 +7990,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8008,10 +8023,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8022,10 +8037,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8033,7 +8048,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8048,24 +8063,26 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O47" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8107,7 +8124,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8128,10 +8145,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8142,10 +8159,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8153,7 +8170,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8168,24 +8185,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8227,7 +8244,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8248,10 +8265,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8262,10 +8279,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8273,7 +8290,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8288,24 +8305,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>82</v>
+        <v>375</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8347,7 +8364,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8368,10 +8385,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8382,10 +8399,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8408,19 +8425,17 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8469,7 +8484,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8490,10 +8505,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8504,10 +8519,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8530,19 +8545,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8591,7 +8606,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8612,10 +8627,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8624,12 +8639,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8637,13 +8652,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8652,19 +8667,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>107</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>378</v>
+        <v>337</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>379</v>
+        <v>338</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>380</v>
+        <v>339</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>381</v>
+        <v>340</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8713,7 +8728,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>376</v>
+        <v>341</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8728,30 +8743,30 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>382</v>
+        <v>82</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>383</v>
+        <v>342</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>384</v>
+        <v>343</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>385</v>
+        <v>82</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53" hidden="true">
+    <row r="53">
       <c r="A53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8759,13 +8774,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8774,18 +8789,20 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="O53" s="2"/>
+        <v>385</v>
+      </c>
+      <c r="O53" t="s" s="2">
+        <v>386</v>
+      </c>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8833,13 +8850,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8848,19 +8865,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>82</v>
+        <v>387</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>349</v>
+        <v>388</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8868,21 +8885,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>82</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8894,20 +8911,18 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="M54" t="s" s="2">
         <v>394</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="M54" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N54" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8955,13 +8970,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8970,44 +8985,44 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>399</v>
+        <v>82</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>400</v>
+        <v>354</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>402</v>
+        <v>390</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9016,19 +9031,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>406</v>
+        <v>400</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>408</v>
+        <v>402</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9077,7 +9092,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>403</v>
+        <v>397</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9086,50 +9101,50 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>410</v>
+        <v>82</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>411</v>
+        <v>105</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56" hidden="true">
+    <row r="56">
       <c r="A56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>82</v>
+        <v>409</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9138,18 +9153,20 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>129</v>
+        <v>410</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="O56" s="2"/>
+        <v>413</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>414</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9197,7 +9214,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9206,25 +9223,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>82</v>
+        <v>415</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>82</v>
+        <v>417</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AO56" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9232,10 +9249,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9246,7 +9263,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9258,18 +9275,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="N57" t="s" s="2">
         <v>424</v>
       </c>
-      <c r="L57" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="N57" s="2"/>
-      <c r="O57" t="s" s="2">
-        <v>427</v>
-      </c>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9317,13 +9334,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9332,19 +9349,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>428</v>
+        <v>82</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9352,10 +9369,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9366,10 +9383,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9378,19 +9395,17 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>435</v>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="N58" s="2"/>
       <c r="O58" t="s" s="2">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9427,59 +9442,59 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="AC58" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>438</v>
+        <v>82</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>82</v>
+        <v>433</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>440</v>
+        <v>82</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>441</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>442</v>
+        <v>435</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>444</v>
+        <v>437</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9500,19 +9515,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9522,7 +9537,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9549,19 +9564,17 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="AC59" s="2"/>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9570,7 +9583,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9579,29 +9592,31 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="60" hidden="true">
+    <row r="60">
       <c r="A60" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>437</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>450</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9613,25 +9628,29 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>107</v>
+        <v>438</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>108</v>
+        <v>439</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>439</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>441</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9640,7 +9659,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>82</v>
+        <v>451</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9679,7 +9698,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>110</v>
+        <v>437</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9688,47 +9707,47 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>82</v>
+        <v>445</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>111</v>
+        <v>447</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9740,17 +9759,15 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N61" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N61" s="2"/>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9787,31 +9804,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9832,48 +9849,46 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>453</v>
+        <v>114</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>454</v>
+        <v>115</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>455</v>
+        <v>116</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>457</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9909,31 +9924,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>458</v>
+        <v>121</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9942,10 +9957,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>459</v>
+        <v>82</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>460</v>
+        <v>111</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9954,12 +9969,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" hidden="true">
+    <row r="63">
       <c r="A63" t="s" s="2">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9967,83 +9982,83 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>173</v>
+        <v>458</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="O63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q63" s="2"/>
+      <c r="R63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="P63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q63" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="R63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="Y63" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10064,10 +10079,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10076,12 +10091,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>472</v>
+        <v>466</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10089,37 +10104,39 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I64" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" s="2"/>
+      <c r="Q64" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10139,13 +10156,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>82</v>
+        <v>253</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>82</v>
+        <v>472</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>82</v>
+        <v>473</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10163,7 +10180,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10184,10 +10201,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10198,10 +10215,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10224,24 +10241,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>485</v>
+        <v>82</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10283,7 +10300,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10292,7 +10309,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>487</v>
+        <v>82</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10304,10 +10321,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10318,10 +10335,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10344,26 +10361,24 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>173</v>
+        <v>135</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>493</v>
-      </c>
+        <v>488</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>82</v>
+        <v>490</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10381,13 +10396,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>248</v>
+        <v>82</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>495</v>
+        <v>82</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>496</v>
+        <v>82</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10405,7 +10420,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10414,7 +10429,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>82</v>
+        <v>492</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10426,10 +10441,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10440,10 +10455,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10451,7 +10466,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10463,22 +10478,22 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>256</v>
+        <v>173</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10503,13 +10518,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>155</v>
+        <v>253</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10527,7 +10542,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10536,7 +10551,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10548,10 +10563,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>196</v>
+        <v>483</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10560,12 +10575,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68" hidden="true">
+    <row r="68">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10579,7 +10594,7 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10588,16 +10603,20 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>107</v>
+        <v>261</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>108</v>
+        <v>505</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+        <v>506</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>508</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10621,13 +10640,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>82</v>
+        <v>509</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>82</v>
+        <v>510</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10645,7 +10664,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>110</v>
+        <v>504</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10654,10 +10673,10 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10666,10 +10685,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>111</v>
+        <v>512</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10680,21 +10699,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10706,17 +10725,15 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N69" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10753,31 +10770,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10800,14 +10817,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10823,23 +10840,21 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>151</v>
+        <v>114</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>274</v>
+        <v>115</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>275</v>
+        <v>116</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="O70" t="s" s="2">
-        <v>277</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10875,19 +10890,19 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>278</v>
+        <v>121</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10899,7 +10914,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10908,10 +10923,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>279</v>
+        <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>280</v>
+        <v>111</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10922,10 +10937,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10936,7 +10951,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10945,19 +10960,23 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>107</v>
+        <v>151</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>108</v>
+        <v>279</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N71" s="2"/>
-      <c r="O71" s="2"/>
+        <v>280</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O71" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11005,19 +11024,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>110</v>
+        <v>283</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>82</v>
+        <v>105</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11026,10 +11045,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>82</v>
+        <v>284</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>111</v>
+        <v>285</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11040,21 +11059,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11066,17 +11085,15 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11113,31 +11130,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11160,21 +11177,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11183,23 +11200,21 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>135</v>
+        <v>114</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>287</v>
+        <v>115</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>288</v>
+        <v>116</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O73" t="s" s="2">
-        <v>290</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11235,31 +11250,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>292</v>
+        <v>121</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11268,10 +11283,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>293</v>
+        <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>294</v>
+        <v>111</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11282,10 +11297,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11293,7 +11308,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -11308,18 +11323,20 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="O74" s="2"/>
+        <v>294</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>295</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11367,7 +11384,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11388,10 +11405,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11402,10 +11419,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11413,7 +11430,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11428,18 +11445,18 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" t="s" s="2">
-        <v>307</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11487,7 +11504,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11508,10 +11525,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11522,10 +11539,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11533,7 +11550,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11548,17 +11565,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11607,7 +11624,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11628,10 +11645,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11642,10 +11659,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11668,19 +11685,17 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>322</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>320</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11729,7 +11744,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11750,10 +11765,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11764,10 +11779,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11790,19 +11805,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>107</v>
+        <v>327</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11851,7 +11866,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11872,10 +11887,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11886,21 +11901,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11909,22 +11924,22 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>256</v>
+        <v>107</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>521</v>
+        <v>337</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>522</v>
+        <v>338</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>523</v>
+        <v>339</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>524</v>
+        <v>340</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11949,11 +11964,13 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11971,13 +11988,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>519</v>
+        <v>341</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -11989,31 +12006,31 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>527</v>
+        <v>342</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>528</v>
+        <v>343</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12032,19 +12049,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>531</v>
+        <v>261</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12069,13 +12086,11 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y80" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y80" s="2"/>
       <c r="Z80" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>82</v>
@@ -12093,7 +12108,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12111,27 +12126,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>82</v>
+        <v>534</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12142,7 +12157,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12154,18 +12169,20 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>256</v>
+        <v>536</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N81" t="s" s="2">
         <v>539</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="N81" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12189,13 +12206,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>542</v>
+        <v>82</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>543</v>
+        <v>82</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12213,13 +12230,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12231,27 +12248,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>544</v>
+        <v>82</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>547</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12265,7 +12282,7 @@
         <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -12274,20 +12291,18 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>552</v>
-      </c>
+        <v>546</v>
+      </c>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12311,11 +12326,13 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y82" s="2"/>
+        <v>163</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>547</v>
+      </c>
       <c r="Z82" t="s" s="2">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>82</v>
@@ -12333,7 +12350,7 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12351,27 +12368,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>82</v>
+        <v>549</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>554</v>
+        <v>550</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>82</v>
+        <v>552</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12385,7 +12402,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12394,18 +12411,20 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="O83" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L83" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12429,13 +12448,11 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y83" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>82</v>
+        <v>558</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12453,7 +12470,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12471,27 +12488,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="AO83" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP83" t="s" s="2">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>565</v>
-      </c>
       <c r="B84" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12505,7 +12522,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12514,16 +12531,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>567</v>
+        <v>563</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>568</v>
+        <v>564</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>569</v>
+        <v>565</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12573,7 +12590,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12591,27 +12608,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AM84" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP84" t="s" s="2">
-        <v>573</v>
-      </c>
-    </row>
-    <row r="85" hidden="true">
-      <c r="A85" t="s" s="2">
-        <v>574</v>
-      </c>
       <c r="B85" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12622,10 +12639,10 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12634,20 +12651,18 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>579</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12695,45 +12710,45 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>580</v>
+        <v>105</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>82</v>
+        <v>575</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>82</v>
+        <v>578</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12744,7 +12759,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12756,16 +12771,20 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>107</v>
+        <v>580</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>108</v>
+        <v>581</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>582</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>584</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12813,19 +12832,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>110</v>
+        <v>579</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>82</v>
+        <v>585</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12834,10 +12853,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>82</v>
+        <v>586</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>111</v>
+        <v>587</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12848,21 +12867,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12874,17 +12893,15 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N87" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12933,19 +12950,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12968,14 +12985,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>586</v>
+        <v>113</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -12988,26 +13005,24 @@
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>587</v>
+        <v>115</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>588</v>
+        <v>116</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O88" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13055,7 +13070,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13079,7 +13094,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13097,26 +13112,26 @@
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>591</v>
+        <v>114</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>592</v>
@@ -13124,8 +13139,12 @@
       <c r="M89" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+      <c r="N89" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>219</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13173,19 +13192,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>594</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13194,10 +13213,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>596</v>
+        <v>196</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13208,10 +13227,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13234,13 +13253,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>591</v>
+        <v>596</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="M90" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13291,7 +13310,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13300,7 +13319,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>594</v>
+        <v>599</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13312,10 +13331,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>595</v>
+        <v>600</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13326,10 +13345,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13352,20 +13371,16 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>256</v>
+        <v>596</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="N91" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="O91" t="s" s="2">
-        <v>605</v>
-      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13389,13 +13404,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13413,7 +13428,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13422,7 +13437,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>82</v>
+        <v>599</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13431,13 +13446,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>608</v>
+        <v>82</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>528</v>
+        <v>605</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13448,10 +13463,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13462,7 +13477,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13474,19 +13489,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13511,13 +13526,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>163</v>
+        <v>177</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>616</v>
+        <v>612</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13535,13 +13550,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13553,13 +13568,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>608</v>
+        <v>613</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>609</v>
+        <v>614</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13570,10 +13585,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13584,7 +13599,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13596,17 +13611,19 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="N93" t="s" s="2">
         <v>618</v>
       </c>
-      <c r="L93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>619</v>
-      </c>
-      <c r="M93" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" t="s" s="2">
-        <v>621</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13631,13 +13648,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>621</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13655,13 +13672,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13673,13 +13690,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>82</v>
+        <v>613</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>82</v>
+        <v>614</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>622</v>
+        <v>533</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13690,10 +13707,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13716,7 +13733,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>623</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>624</v>
@@ -13725,7 +13742,9 @@
         <v>625</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>626</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13773,7 +13792,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13794,10 +13813,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>595</v>
+        <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13808,10 +13827,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13822,7 +13841,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13831,10 +13850,10 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>628</v>
+        <v>107</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>629</v>
@@ -13842,9 +13861,7 @@
       <c r="M95" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N95" t="s" s="2">
-        <v>631</v>
-      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13893,13 +13910,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13914,10 +13931,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>632</v>
+        <v>600</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13928,10 +13945,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13954,16 +13971,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>633</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="M96" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="M96" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>638</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14013,7 +14030,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14034,24 +14051,24 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>632</v>
+        <v>637</v>
       </c>
       <c r="AN96" t="s" s="2">
+        <v>638</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
         <v>639</v>
       </c>
-      <c r="AO96" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP96" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>640</v>
-      </c>
       <c r="B97" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14065,7 +14082,7 @@
         <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14074,20 +14091,18 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>575</v>
+        <v>640</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>641</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>642</v>
-      </c>
-      <c r="O97" t="s" s="2">
         <v>643</v>
       </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14135,7 +14150,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14147,33 +14162,33 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>637</v>
+      </c>
+      <c r="AN97" t="s" s="2">
         <v>644</v>
       </c>
-      <c r="AK97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM97" t="s" s="2">
+      <c r="AO97" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s" s="2">
         <v>645</v>
       </c>
-      <c r="AN97" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="AO97" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP97" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="98" hidden="true">
-      <c r="A98" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="B98" t="s" s="2">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14184,28 +14199,32 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>107</v>
+        <v>580</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>108</v>
+        <v>646</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N98" s="2"/>
-      <c r="O98" s="2"/>
+        <v>646</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="O98" t="s" s="2">
+        <v>648</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14253,19 +14272,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>110</v>
+        <v>645</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>82</v>
+        <v>649</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14274,10 +14293,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>82</v>
+        <v>650</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>111</v>
+        <v>651</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14288,21 +14307,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14314,17 +14333,15 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N99" s="2"/>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14373,19 +14390,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14408,14 +14425,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>586</v>
+        <v>113</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14428,26 +14445,24 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>587</v>
+        <v>115</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>588</v>
+        <v>116</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" t="s" s="2">
-        <v>214</v>
-      </c>
+      <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14495,7 +14510,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>589</v>
+        <v>121</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14519,7 +14534,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>196</v>
+        <v>111</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14528,47 +14543,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>82</v>
+        <v>591</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H101" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I101" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>256</v>
+        <v>114</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>651</v>
+        <v>592</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>652</v>
+        <v>593</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>653</v>
+        <v>117</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>654</v>
+        <v>219</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14593,13 +14608,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>346</v>
+        <v>82</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14617,34 +14632,34 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>650</v>
+        <v>594</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>655</v>
+        <v>82</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>350</v>
+        <v>196</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14652,10 +14667,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14663,7 +14678,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14678,19 +14693,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="L102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="O102" t="s" s="2">
         <v>659</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>660</v>
-      </c>
-      <c r="O102" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14718,10 +14733,10 @@
         <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>661</v>
+        <v>350</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>662</v>
+        <v>351</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14739,16 +14754,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>663</v>
+        <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14757,27 +14772,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>441</v>
+        <v>354</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>442</v>
+        <v>355</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>82</v>
+        <v>356</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14797,22 +14812,22 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>256</v>
+        <v>662</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>666</v>
+        <v>663</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>503</v>
+        <v>441</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14840,10 +14855,10 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>504</v>
+        <v>666</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>505</v>
+        <v>667</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14861,7 +14876,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>665</v>
+        <v>661</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14870,7 +14885,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14879,22 +14894,22 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>82</v>
+        <v>669</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>196</v>
+        <v>446</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>507</v>
+        <v>447</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>82</v>
+        <v>448</v>
       </c>
     </row>
-    <row r="104" hidden="true">
+    <row r="104">
       <c r="A104" t="s" s="2">
         <v>670</v>
       </c>
@@ -14903,17 +14918,17 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>520</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14922,19 +14937,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>521</v>
+        <v>671</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>522</v>
+        <v>672</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>523</v>
+        <v>673</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14962,10 +14977,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>671</v>
+        <v>509</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>525</v>
+        <v>510</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14989,10 +15004,10 @@
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>82</v>
+        <v>674</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15001,31 +15016,31 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>526</v>
+        <v>82</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>527</v>
+        <v>196</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15044,19 +15059,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>83</v>
+        <v>261</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>673</v>
+        <v>526</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>674</v>
+        <v>527</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>578</v>
+        <v>528</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>579</v>
+        <v>529</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15081,13 +15096,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>82</v>
+        <v>530</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15105,7 +15120,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15123,23 +15138,145 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>531</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>581</v>
+        <v>532</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>582</v>
+        <v>533</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>678</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="O106" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="P106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>105</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP106" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP105">
+  <autoFilter ref="A1:AP106">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15149,7 +15286,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI104">
+  <conditionalFormatting sqref="A2:AI105">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$106</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$105</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4092" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4054" uniqueCount="675">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-13T07:29:03+00:00</t>
+    <t>2026-01-29T14:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -676,22 +676,6 @@
 Texte libre (ex. diabète, surpoids, hypercholestérolémie, risque cardiovasculaire, suivi, ...)</t>
   </si>
   <si>
-    <t>Observation.extension:MesOriginOfData</t>
-  </si>
-  <si>
-    <t>MesOriginOfData</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/mesures/StructureDefinition/mesures-origin-of-data}
-</t>
-  </si>
-  <si>
-    <t>Origine de la donnée</t>
-  </si>
-  <si>
-    <t>Extension pour tracer l'origine de la donnée issue d'un compte rendu de biologie (CR-Bio).</t>
-  </si>
-  <si>
     <t>Observation.modifierExtension</t>
   </si>
   <si>
@@ -1350,7 +1334,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -2455,7 +2439,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP106"/>
+  <dimension ref="A1:AP105"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="45.33984375" customWidth="true" bestFit="true"/>
@@ -2468,7 +2452,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="179.3984375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="232.12890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4908,41 +4892,43 @@
         <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>197</v>
-      </c>
-      <c r="C21" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J21" t="s" s="2">
         <v>82</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>213</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="N21" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="O21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="M21" t="s" s="2">
-        <v>215</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>82</v>
       </c>
@@ -4990,7 +4976,7 @@
         <v>82</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -5014,7 +5000,7 @@
         <v>82</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>82</v>
+        <v>196</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>82</v>
@@ -5032,7 +5018,7 @@
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -5045,25 +5031,23 @@
         <v>82</v>
       </c>
       <c r="I22" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J22" t="s" s="2">
         <v>94</v>
       </c>
-      <c r="J22" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K22" t="s" s="2">
-        <v>114</v>
+        <v>217</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>117</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>82</v>
@@ -5112,7 +5096,7 @@
         <v>82</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -5124,22 +5108,22 @@
         <v>82</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>82</v>
+        <v>221</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>82</v>
+        <v>222</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>82</v>
+        <v>224</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>82</v>
@@ -5147,14 +5131,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>82</v>
+        <v>226</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5173,17 +5157,17 @@
         <v>94</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>82</v>
@@ -5232,7 +5216,7 @@
         <v>82</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5247,19 +5231,19 @@
         <v>105</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>229</v>
+        <v>82</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>82</v>
@@ -5267,14 +5251,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5293,18 +5277,18 @@
         <v>94</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="N24" s="2"/>
-      <c r="O24" t="s" s="2">
-        <v>235</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
         <v>82</v>
       </c>
@@ -5352,7 +5336,7 @@
         <v>82</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5367,16 +5351,16 @@
         <v>105</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>82</v>
@@ -5385,46 +5369,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>240</v>
+        <v>82</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J25" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>173</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>244</v>
-      </c>
-      <c r="O25" s="2"/>
+        <v>246</v>
+      </c>
+      <c r="O25" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="P25" t="s" s="2">
         <v>82</v>
       </c>
@@ -5448,13 +5434,11 @@
         <v>82</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y25" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>82</v>
+        <v>249</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>82</v>
@@ -5472,13 +5456,13 @@
         <v>82</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>82</v>
@@ -5487,30 +5471,30 @@
         <v>105</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>82</v>
+        <v>251</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>82</v>
+        <v>254</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5521,31 +5505,31 @@
         <v>93</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>94</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>82</v>
@@ -5570,35 +5554,35 @@
         <v>82</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="Y26" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>261</v>
+      </c>
       <c r="Z26" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC26" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>263</v>
+      </c>
+      <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>82</v>
@@ -5607,32 +5591,34 @@
         <v>105</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AM26" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO26" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP26" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="B27" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AL26" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="AP26" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="27" hidden="true">
-      <c r="A27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C27" s="2"/>
+      <c r="C27" t="s" s="2">
+        <v>267</v>
+      </c>
       <c r="D27" t="s" s="2">
         <v>82</v>
       </c>
@@ -5641,7 +5627,7 @@
         <v>93</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>94</v>
@@ -5653,19 +5639,19 @@
         <v>82</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>82</v>
@@ -5693,26 +5679,28 @@
         <v>177</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB27" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="AC27" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD27" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5736,37 +5724,35 @@
         <v>82</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AP27" t="s" s="2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
+        <v>268</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>269</v>
       </c>
-      <c r="AO27" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AP27" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>260</v>
-      </c>
-      <c r="C28" t="s" s="2">
-        <v>272</v>
-      </c>
+      <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>82</v>
@@ -5775,20 +5761,16 @@
         <v>82</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>262</v>
+        <v>108</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N28" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>82</v>
       </c>
@@ -5812,13 +5794,13 @@
         <v>82</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>266</v>
+        <v>82</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>267</v>
+        <v>82</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>82</v>
@@ -5836,19 +5818,19 @@
         <v>82</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>260</v>
+        <v>110</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>82</v>
@@ -5860,10 +5842,10 @@
         <v>82</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>269</v>
+        <v>111</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>270</v>
+        <v>82</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>82</v>
@@ -5871,21 +5853,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>82</v>
@@ -5897,15 +5879,17 @@
         <v>82</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N29" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N29" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>82</v>
@@ -5942,31 +5926,31 @@
         <v>82</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>82</v>
@@ -5987,46 +5971,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>81</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>82</v>
       </c>
@@ -6062,19 +6048,19 @@
         <v>82</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -6086,7 +6072,7 @@
         <v>82</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>82</v>
@@ -6095,10 +6081,10 @@
         <v>82</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>82</v>
@@ -6107,12 +6093,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6120,35 +6106,31 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G31" t="s" s="2">
         <v>93</v>
       </c>
-      <c r="G31" t="s" s="2">
-        <v>81</v>
-      </c>
       <c r="H31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>82</v>
       </c>
@@ -6196,19 +6178,19 @@
         <v>82</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>82</v>
@@ -6217,10 +6199,10 @@
         <v>82</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>82</v>
@@ -6231,21 +6213,21 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>82</v>
@@ -6257,15 +6239,17 @@
         <v>82</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>82</v>
@@ -6302,31 +6286,31 @@
         <v>82</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>82</v>
@@ -6347,52 +6331,54 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O33" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>82</v>
+        <v>291</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>82</v>
@@ -6422,31 +6408,31 @@
         <v>82</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK33" t="s" s="2">
         <v>82</v>
@@ -6455,10 +6441,10 @@
         <v>82</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>82</v>
@@ -6467,12 +6453,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6480,13 +6466,13 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>82</v>
@@ -6495,26 +6481,24 @@
         <v>94</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q34" s="2"/>
       <c r="R34" t="s" s="2">
-        <v>296</v>
+        <v>82</v>
       </c>
       <c r="S34" t="s" s="2">
         <v>82</v>
@@ -6556,7 +6540,7 @@
         <v>82</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6577,10 +6561,10 @@
         <v>82</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>82</v>
@@ -6589,12 +6573,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6602,13 +6586,13 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>82</v>
@@ -6617,24 +6601,24 @@
         <v>94</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O35" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>82</v>
+        <v>308</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>82</v>
@@ -6676,7 +6660,7 @@
         <v>82</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6697,10 +6681,10 @@
         <v>82</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>82</v>
@@ -6709,12 +6693,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6722,13 +6706,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>82</v>
@@ -6737,24 +6721,24 @@
         <v>94</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>313</v>
+        <v>82</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>82</v>
@@ -6796,7 +6780,7 @@
         <v>82</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6817,10 +6801,10 @@
         <v>82</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>82</v>
@@ -6831,10 +6815,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6857,17 +6841,19 @@
         <v>94</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O37" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>82</v>
@@ -6916,7 +6902,7 @@
         <v>82</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6937,10 +6923,10 @@
         <v>82</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>82</v>
@@ -6951,10 +6937,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6977,19 +6963,19 @@
         <v>94</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>82</v>
@@ -7038,7 +7024,7 @@
         <v>82</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -7059,10 +7045,10 @@
         <v>82</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>82</v>
@@ -7071,26 +7057,26 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>340</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>82</v>
@@ -7099,19 +7085,19 @@
         <v>94</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>82</v>
@@ -7136,13 +7122,13 @@
         <v>82</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>82</v>
@@ -7160,10 +7146,10 @@
         <v>82</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH39" t="s" s="2">
         <v>93</v>
@@ -7175,66 +7161,62 @@
         <v>105</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>82</v>
+        <v>347</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>82</v>
+        <v>348</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>82</v>
+        <v>352</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>345</v>
+        <v>82</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G40" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>346</v>
+        <v>108</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N40" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O40" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>82</v>
       </c>
@@ -7258,13 +7240,13 @@
         <v>82</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>350</v>
+        <v>82</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>351</v>
+        <v>82</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>82</v>
@@ -7282,10 +7264,10 @@
         <v>82</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>344</v>
+        <v>110</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH40" t="s" s="2">
         <v>93</v>
@@ -7294,44 +7276,44 @@
         <v>82</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>352</v>
+        <v>82</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>353</v>
+        <v>82</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>354</v>
+        <v>82</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>355</v>
+        <v>111</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>357</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>82</v>
@@ -7343,15 +7325,17 @@
         <v>82</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>82</v>
@@ -7388,31 +7372,31 @@
         <v>82</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>82</v>
@@ -7435,18 +7419,18 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G42" t="s" s="2">
         <v>81</v>
@@ -7458,21 +7442,23 @@
         <v>82</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O42" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O42" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7508,11 +7494,9 @@
         <v>82</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>119</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
         <v>82</v>
       </c>
@@ -7520,7 +7504,7 @@
         <v>120</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7532,7 +7516,7 @@
         <v>82</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>82</v>
@@ -7541,10 +7525,10 @@
         <v>82</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>82</v>
@@ -7555,12 +7539,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="C43" t="s" s="2">
+        <v>358</v>
+      </c>
       <c r="D43" t="s" s="2">
         <v>82</v>
       </c>
@@ -7569,7 +7555,7 @@
         <v>93</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>82</v>
@@ -7584,16 +7570,16 @@
         <v>151</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>82</v>
@@ -7630,17 +7616,19 @@
         <v>82</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>361</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7661,10 +7649,10 @@
         <v>82</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>82</v>
@@ -7675,20 +7663,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="C44" t="s" s="2">
-        <v>363</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>93</v>
@@ -7700,23 +7686,19 @@
         <v>82</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O44" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>82</v>
       </c>
@@ -7764,19 +7746,19 @@
         <v>82</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>82</v>
@@ -7785,10 +7767,10 @@
         <v>82</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO44" t="s" s="2">
         <v>82</v>
@@ -7799,21 +7781,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>82</v>
@@ -7825,15 +7807,17 @@
         <v>82</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>82</v>
@@ -7870,31 +7854,31 @@
         <v>82</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>82</v>
@@ -7917,21 +7901,21 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>82</v>
@@ -7940,27 +7924,29 @@
         <v>82</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>82</v>
+        <v>365</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>82</v>
@@ -7990,31 +7976,31 @@
         <v>82</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>82</v>
@@ -8023,10 +8009,10 @@
         <v>82</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>82</v>
@@ -8037,10 +8023,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8048,7 +8034,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>93</v>
@@ -8063,26 +8049,24 @@
         <v>94</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q47" s="2"/>
       <c r="R47" t="s" s="2">
-        <v>370</v>
+        <v>82</v>
       </c>
       <c r="S47" t="s" s="2">
         <v>82</v>
@@ -8124,7 +8108,7 @@
         <v>82</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -8145,10 +8129,10 @@
         <v>82</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>82</v>
@@ -8159,10 +8143,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8170,7 +8154,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>93</v>
@@ -8185,24 +8169,24 @@
         <v>94</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O48" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>82</v>
+        <v>370</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>82</v>
@@ -8244,7 +8228,7 @@
         <v>82</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -8265,10 +8249,10 @@
         <v>82</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>82</v>
@@ -8279,10 +8263,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8290,7 +8274,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>93</v>
@@ -8305,24 +8289,24 @@
         <v>94</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q49" s="2"/>
       <c r="R49" t="s" s="2">
-        <v>375</v>
+        <v>82</v>
       </c>
       <c r="S49" t="s" s="2">
         <v>82</v>
@@ -8364,7 +8348,7 @@
         <v>82</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -8385,10 +8369,10 @@
         <v>82</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>82</v>
@@ -8399,10 +8383,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8425,17 +8409,19 @@
         <v>94</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O50" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>82</v>
@@ -8484,7 +8470,7 @@
         <v>82</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -8505,10 +8491,10 @@
         <v>82</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>82</v>
@@ -8519,10 +8505,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8545,19 +8531,19 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>82</v>
@@ -8606,7 +8592,7 @@
         <v>82</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8627,10 +8613,10 @@
         <v>82</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>82</v>
@@ -8639,12 +8625,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8652,13 +8638,13 @@
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H52" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I52" t="s" s="2">
         <v>82</v>
@@ -8667,19 +8653,19 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>377</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>338</v>
+        <v>379</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>339</v>
+        <v>380</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>82</v>
@@ -8728,7 +8714,7 @@
         <v>82</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>341</v>
+        <v>376</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8743,30 +8729,30 @@
         <v>105</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>82</v>
+        <v>382</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>342</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>343</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>82</v>
+        <v>385</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8774,13 +8760,13 @@
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>82</v>
@@ -8789,20 +8775,18 @@
         <v>94</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="O53" t="s" s="2">
-        <v>386</v>
-      </c>
+        <v>390</v>
+      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>82</v>
       </c>
@@ -8850,13 +8834,13 @@
         <v>82</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>82</v>
@@ -8865,19 +8849,19 @@
         <v>105</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>387</v>
+        <v>82</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>388</v>
+        <v>349</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>82</v>
@@ -8885,21 +8869,21 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>82</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>82</v>
@@ -8911,18 +8895,20 @@
         <v>94</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="O54" s="2"/>
+        <v>397</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>82</v>
       </c>
@@ -8970,13 +8956,13 @@
         <v>82</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>82</v>
@@ -8985,44 +8971,44 @@
         <v>105</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>82</v>
+        <v>399</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>354</v>
+        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>396</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G55" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>82</v>
@@ -9031,19 +9017,19 @@
         <v>94</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>82</v>
@@ -9092,7 +9078,7 @@
         <v>82</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9101,50 +9087,50 @@
         <v>93</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>82</v>
+        <v>410</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>105</v>
+        <v>411</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>82</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>409</v>
+        <v>82</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G56" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>82</v>
@@ -9153,20 +9139,18 @@
         <v>94</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>129</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>414</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>82</v>
       </c>
@@ -9214,7 +9198,7 @@
         <v>82</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9223,25 +9207,25 @@
         <v>93</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>415</v>
+        <v>82</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>416</v>
+        <v>105</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>417</v>
+        <v>82</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>82</v>
@@ -9249,10 +9233,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9263,7 +9247,7 @@
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>82</v>
@@ -9275,18 +9259,18 @@
         <v>94</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>129</v>
+        <v>424</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="O57" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" t="s" s="2">
+        <v>427</v>
+      </c>
       <c r="P57" t="s" s="2">
         <v>82</v>
       </c>
@@ -9334,13 +9318,13 @@
         <v>82</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>82</v>
@@ -9349,19 +9333,19 @@
         <v>105</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>82</v>
+        <v>428</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>82</v>
@@ -9369,10 +9353,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9383,10 +9367,10 @@
         <v>80</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>82</v>
@@ -9395,17 +9379,19 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N58" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>435</v>
+      </c>
       <c r="O58" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>82</v>
@@ -9442,59 +9428,59 @@
         <v>82</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>437</v>
+      </c>
+      <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>82</v>
+        <v>438</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>82</v>
+        <v>439</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>105</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>433</v>
+        <v>82</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>82</v>
+        <v>440</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>441</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>437</v>
+        <v>444</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C59" s="2"/>
+        <v>432</v>
+      </c>
+      <c r="C59" t="s" s="2">
+        <v>445</v>
+      </c>
       <c r="D59" t="s" s="2">
         <v>82</v>
       </c>
@@ -9515,19 +9501,19 @@
         <v>94</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>82</v>
@@ -9537,7 +9523,7 @@
         <v>82</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>82</v>
+        <v>446</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>82</v>
@@ -9564,17 +9550,19 @@
         <v>82</v>
       </c>
       <c r="AB59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AC59" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="AD59" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>443</v>
+        <v>82</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9583,7 +9571,7 @@
         <v>93</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>105</v>
@@ -9592,31 +9580,29 @@
         <v>82</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="AN59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AO59" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AP59" t="s" s="2">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="AO59" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP59" t="s" s="2">
+      <c r="B60" t="s" s="2">
         <v>448</v>
       </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="C60" t="s" s="2">
-        <v>450</v>
-      </c>
+      <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9628,29 +9614,25 @@
         <v>93</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>438</v>
+        <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>439</v>
+        <v>108</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>441</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>82</v>
       </c>
@@ -9659,7 +9641,7 @@
         <v>82</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>451</v>
+        <v>82</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>82</v>
@@ -9698,7 +9680,7 @@
         <v>82</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>437</v>
+        <v>110</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9707,47 +9689,47 @@
         <v>93</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>445</v>
+        <v>82</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>446</v>
+        <v>82</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>447</v>
+        <v>111</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>82</v>
@@ -9759,15 +9741,17 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>82</v>
@@ -9804,31 +9788,31 @@
         <v>82</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>82</v>
@@ -9849,46 +9833,48 @@
         <v>82</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J62" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>114</v>
+        <v>453</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>115</v>
+        <v>454</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>116</v>
+        <v>455</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>456</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>457</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>82</v>
       </c>
@@ -9924,31 +9910,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>121</v>
+        <v>458</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>82</v>
@@ -9957,10 +9943,10 @@
         <v>82</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>82</v>
+        <v>459</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>111</v>
+        <v>460</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>82</v>
@@ -9969,12 +9955,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9982,39 +9968,39 @@
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H63" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I63" t="s" s="2">
         <v>94</v>
-      </c>
-      <c r="I63" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>458</v>
+        <v>173</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>461</v>
-      </c>
+        <v>464</v>
+      </c>
+      <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q63" s="2"/>
+      <c r="Q63" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="R63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10034,13 +10020,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>82</v>
+        <v>468</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10058,7 +10044,7 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10079,10 +10065,10 @@
         <v>82</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10091,12 +10077,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10104,39 +10090,37 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G64" t="s" s="2">
         <v>93</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
-      <c r="Q64" t="s" s="2">
-        <v>471</v>
-      </c>
+      <c r="Q64" s="2"/>
       <c r="R64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10156,13 +10140,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>472</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>473</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10180,7 +10164,7 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10201,10 +10185,10 @@
         <v>82</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>82</v>
@@ -10215,10 +10199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10241,24 +10225,24 @@
         <v>94</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>82</v>
+        <v>485</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>82</v>
@@ -10300,7 +10284,7 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10309,7 +10293,7 @@
         <v>93</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>82</v>
+        <v>487</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>105</v>
@@ -10321,10 +10305,10 @@
         <v>82</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10335,10 +10319,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10361,24 +10345,26 @@
         <v>94</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="N66" s="2"/>
+        <v>492</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>493</v>
+      </c>
       <c r="O66" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
-        <v>490</v>
+        <v>82</v>
       </c>
       <c r="S66" t="s" s="2">
         <v>82</v>
@@ -10396,13 +10382,13 @@
         <v>82</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>82</v>
+        <v>248</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>82</v>
+        <v>495</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>82</v>
+        <v>496</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>82</v>
@@ -10420,7 +10406,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10429,7 +10415,7 @@
         <v>93</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>492</v>
+        <v>82</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>105</v>
@@ -10441,10 +10427,10 @@
         <v>82</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10455,10 +10441,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10466,7 +10452,7 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>93</v>
@@ -10478,22 +10464,22 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>173</v>
+        <v>256</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>82</v>
@@ -10518,13 +10504,13 @@
         <v>82</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>253</v>
+        <v>155</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>82</v>
@@ -10542,7 +10528,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10551,7 +10537,7 @@
         <v>93</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>82</v>
+        <v>506</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>105</v>
@@ -10563,10 +10549,10 @@
         <v>82</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>483</v>
+        <v>196</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>82</v>
@@ -10575,12 +10561,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10594,7 +10580,7 @@
         <v>93</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>82</v>
@@ -10603,20 +10589,16 @@
         <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>261</v>
+        <v>107</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>505</v>
+        <v>108</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>508</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10640,13 +10622,13 @@
         <v>82</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>509</v>
+        <v>82</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>510</v>
+        <v>82</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>82</v>
@@ -10664,7 +10646,7 @@
         <v>82</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>504</v>
+        <v>110</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10673,10 +10655,10 @@
         <v>93</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>82</v>
@@ -10685,10 +10667,10 @@
         <v>82</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>196</v>
+        <v>82</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>512</v>
+        <v>111</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>82</v>
@@ -10699,21 +10681,21 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
@@ -10725,15 +10707,17 @@
         <v>82</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10770,31 +10754,31 @@
         <v>82</v>
       </c>
       <c r="AB69" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC69" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE69" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>82</v>
@@ -10817,14 +10801,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10840,21 +10824,23 @@
         <v>82</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>115</v>
+        <v>274</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>116</v>
+        <v>275</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O70" s="2"/>
+        <v>276</v>
+      </c>
+      <c r="O70" t="s" s="2">
+        <v>277</v>
+      </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
       </c>
@@ -10890,19 +10876,19 @@
         <v>82</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC70" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD70" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>121</v>
+        <v>278</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10914,7 +10900,7 @@
         <v>82</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>82</v>
@@ -10923,10 +10909,10 @@
         <v>82</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>82</v>
+        <v>279</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>111</v>
+        <v>280</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10937,10 +10923,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10951,7 +10937,7 @@
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>82</v>
@@ -10960,23 +10946,19 @@
         <v>82</v>
       </c>
       <c r="J71" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>151</v>
+        <v>107</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>279</v>
+        <v>108</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>280</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>281</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>282</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -11024,19 +11006,19 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>283</v>
+        <v>110</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>105</v>
+        <v>82</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>82</v>
@@ -11045,10 +11027,10 @@
         <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>284</v>
+        <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>285</v>
+        <v>111</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11059,21 +11041,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11085,15 +11067,17 @@
         <v>82</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11130,31 +11114,31 @@
         <v>82</v>
       </c>
       <c r="AB72" t="s" s="2">
-        <v>82</v>
+        <v>118</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>82</v>
@@ -11177,21 +11161,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>113</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>82</v>
@@ -11200,21 +11184,23 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>115</v>
+        <v>287</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>116</v>
+        <v>288</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O73" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="O73" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="P73" t="s" s="2">
         <v>82</v>
       </c>
@@ -11250,31 +11236,31 @@
         <v>82</v>
       </c>
       <c r="AB73" t="s" s="2">
-        <v>118</v>
+        <v>82</v>
       </c>
       <c r="AC73" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AD73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE73" t="s" s="2">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>121</v>
+        <v>292</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>82</v>
@@ -11283,10 +11269,10 @@
         <v>82</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>82</v>
+        <v>293</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>111</v>
+        <v>294</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11297,10 +11283,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11308,7 +11294,7 @@
       </c>
       <c r="E74" s="2"/>
       <c r="F74" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
         <v>93</v>
@@ -11323,20 +11309,18 @@
         <v>94</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>295</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>82</v>
       </c>
@@ -11384,7 +11368,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11405,10 +11389,10 @@
         <v>82</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11419,10 +11403,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11430,7 +11414,7 @@
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>93</v>
@@ -11445,18 +11429,18 @@
         <v>94</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>107</v>
+        <v>173</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O75" s="2"/>
+        <v>306</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" t="s" s="2">
+        <v>307</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
       </c>
@@ -11504,7 +11488,7 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11525,10 +11509,10 @@
         <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11539,10 +11523,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11550,7 +11534,7 @@
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>93</v>
@@ -11565,17 +11549,17 @@
         <v>94</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" t="s" s="2">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11624,7 +11608,7 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11645,10 +11629,10 @@
         <v>82</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11659,10 +11643,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11685,17 +11669,19 @@
         <v>94</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>322</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N77" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O77" t="s" s="2">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>82</v>
@@ -11744,7 +11730,7 @@
         <v>82</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11765,10 +11751,10 @@
         <v>82</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>82</v>
@@ -11779,10 +11765,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11805,19 +11791,19 @@
         <v>94</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>327</v>
+        <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>82</v>
@@ -11866,7 +11852,7 @@
         <v>82</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11887,10 +11873,10 @@
         <v>82</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>82</v>
@@ -11901,21 +11887,21 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
@@ -11924,22 +11910,22 @@
         <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>107</v>
+        <v>256</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>337</v>
+        <v>521</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>338</v>
+        <v>522</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>339</v>
+        <v>523</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>340</v>
+        <v>524</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>82</v>
@@ -11964,13 +11950,11 @@
         <v>82</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y79" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y79" s="2"/>
       <c r="Z79" t="s" s="2">
-        <v>82</v>
+        <v>525</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11988,13 +11972,13 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>341</v>
+        <v>519</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>82</v>
@@ -12006,31 +11990,31 @@
         <v>82</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>342</v>
+        <v>527</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>343</v>
+        <v>528</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -12049,19 +12033,19 @@
         <v>82</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>261</v>
+        <v>531</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12086,29 +12070,31 @@
         <v>82</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y80" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF80" t="s" s="2">
         <v>530</v>
-      </c>
-      <c r="AA80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE80" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF80" t="s" s="2">
-        <v>524</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12126,27 +12112,27 @@
         <v>82</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>534</v>
+        <v>82</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12157,7 +12143,7 @@
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
@@ -12169,20 +12155,18 @@
         <v>82</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>536</v>
+        <v>256</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>540</v>
-      </c>
+        <v>541</v>
+      </c>
+      <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12206,13 +12190,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>163</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>542</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>543</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12230,13 +12214,13 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>82</v>
@@ -12248,27 +12232,27 @@
         <v>82</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>82</v>
+        <v>547</v>
       </c>
     </row>
-    <row r="82" hidden="true">
+    <row r="82">
       <c r="A82" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12282,7 +12266,7 @@
         <v>93</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I82" t="s" s="2">
         <v>82</v>
@@ -12291,18 +12275,20 @@
         <v>82</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>552</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>82</v>
       </c>
@@ -12326,31 +12312,29 @@
         <v>82</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>547</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="AF82" t="s" s="2">
         <v>548</v>
-      </c>
-      <c r="AA82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE82" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF82" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12368,27 +12352,27 @@
         <v>82</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>549</v>
+        <v>82</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12402,7 +12386,7 @@
         <v>93</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>82</v>
@@ -12411,20 +12395,18 @@
         <v>82</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>261</v>
+        <v>557</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>557</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>82</v>
       </c>
@@ -12448,11 +12430,13 @@
         <v>82</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>155</v>
-      </c>
-      <c r="Y83" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z83" t="s" s="2">
-        <v>558</v>
+        <v>82</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>82</v>
@@ -12470,7 +12454,7 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12488,27 +12472,27 @@
         <v>82</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>82</v>
+        <v>564</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12522,7 +12506,7 @@
         <v>93</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>82</v>
@@ -12531,16 +12515,16 @@
         <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12590,7 +12574,7 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12608,27 +12592,27 @@
         <v>82</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12639,10 +12623,10 @@
         <v>80</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H85" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I85" t="s" s="2">
         <v>82</v>
@@ -12651,18 +12635,20 @@
         <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>578</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>579</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12710,45 +12696,45 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>105</v>
+        <v>580</v>
       </c>
       <c r="AK85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>575</v>
+        <v>82</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>576</v>
+        <v>581</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>577</v>
+        <v>582</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>578</v>
+        <v>82</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12759,7 +12745,7 @@
         <v>80</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>82</v>
@@ -12771,20 +12757,16 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>580</v>
+        <v>107</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>581</v>
+        <v>108</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>584</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12832,19 +12814,19 @@
         <v>82</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>579</v>
+        <v>110</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>585</v>
+        <v>82</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>82</v>
@@ -12853,10 +12835,10 @@
         <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>586</v>
+        <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>587</v>
+        <v>111</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12867,21 +12849,21 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>588</v>
+        <v>584</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
@@ -12893,15 +12875,17 @@
         <v>82</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N87" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
         <v>82</v>
@@ -12950,19 +12934,19 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK87" t="s" s="2">
         <v>82</v>
@@ -12985,14 +12969,14 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>589</v>
+        <v>585</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>113</v>
+        <v>586</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
@@ -13005,24 +12989,26 @@
         <v>82</v>
       </c>
       <c r="I88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K88" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>115</v>
+        <v>587</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>116</v>
+        <v>588</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>82</v>
       </c>
@@ -13070,7 +13056,7 @@
         <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>121</v>
+        <v>589</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -13094,7 +13080,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -13112,26 +13098,26 @@
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>114</v>
+        <v>591</v>
       </c>
       <c r="L89" t="s" s="2">
         <v>592</v>
@@ -13139,12 +13125,8 @@
       <c r="M89" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="N89" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="O89" t="s" s="2">
-        <v>219</v>
-      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13192,19 +13174,19 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>93</v>
+      </c>
+      <c r="AI89" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="AG89" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH89" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI89" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AJ89" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK89" t="s" s="2">
         <v>82</v>
@@ -13213,10 +13195,10 @@
         <v>82</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>196</v>
+        <v>596</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13227,10 +13209,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13253,13 +13235,13 @@
         <v>82</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>596</v>
+        <v>591</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13310,7 +13292,7 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -13319,7 +13301,7 @@
         <v>93</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>105</v>
@@ -13331,10 +13313,10 @@
         <v>82</v>
       </c>
       <c r="AM90" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>600</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>601</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13345,10 +13327,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13371,16 +13353,20 @@
         <v>82</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>596</v>
+        <v>256</v>
       </c>
       <c r="L91" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="M91" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>604</v>
       </c>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" t="s" s="2">
+        <v>605</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13404,13 +13390,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>82</v>
+        <v>177</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>82</v>
+        <v>606</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13428,7 +13414,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13437,7 +13423,7 @@
         <v>93</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>599</v>
+        <v>82</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>105</v>
@@ -13446,13 +13432,13 @@
         <v>82</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>82</v>
+        <v>608</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>600</v>
+        <v>609</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>605</v>
+        <v>528</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13463,10 +13449,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13477,7 +13463,7 @@
         <v>80</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>82</v>
@@ -13489,19 +13475,19 @@
         <v>82</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>82</v>
@@ -13526,13 +13512,13 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13550,13 +13536,13 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>82</v>
@@ -13568,13 +13554,13 @@
         <v>82</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>613</v>
+        <v>608</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>614</v>
+        <v>609</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13585,10 +13571,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13599,7 +13585,7 @@
         <v>80</v>
       </c>
       <c r="G93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H93" t="s" s="2">
         <v>82</v>
@@ -13611,19 +13597,17 @@
         <v>82</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>261</v>
+        <v>618</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>618</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>82</v>
@@ -13648,13 +13632,13 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>620</v>
+        <v>82</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>621</v>
+        <v>82</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13672,13 +13656,13 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH93" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI93" t="s" s="2">
         <v>82</v>
@@ -13690,13 +13674,13 @@
         <v>82</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>613</v>
+        <v>82</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>614</v>
+        <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>533</v>
+        <v>622</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13707,10 +13691,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13733,7 +13717,7 @@
         <v>82</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>623</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
         <v>624</v>
@@ -13742,9 +13726,7 @@
         <v>625</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>626</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13792,7 +13774,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13813,10 +13795,10 @@
         <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>82</v>
+        <v>595</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13827,10 +13809,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13841,7 +13823,7 @@
         <v>80</v>
       </c>
       <c r="G95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H95" t="s" s="2">
         <v>82</v>
@@ -13850,10 +13832,10 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>107</v>
+        <v>628</v>
       </c>
       <c r="L95" t="s" s="2">
         <v>629</v>
@@ -13861,7 +13843,9 @@
       <c r="M95" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="N95" s="2"/>
+      <c r="N95" t="s" s="2">
+        <v>631</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13910,13 +13894,13 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH95" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI95" t="s" s="2">
         <v>82</v>
@@ -13931,10 +13915,10 @@
         <v>82</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>600</v>
+        <v>632</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13945,10 +13929,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13971,16 +13955,16 @@
         <v>94</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -14030,7 +14014,7 @@
         <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
@@ -14051,10 +14035,10 @@
         <v>82</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>637</v>
+        <v>632</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -14063,12 +14047,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="97" hidden="true">
+    <row r="97">
       <c r="A97" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -14082,7 +14066,7 @@
         <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>82</v>
@@ -14091,18 +14075,20 @@
         <v>94</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>640</v>
+        <v>575</v>
       </c>
       <c r="L97" t="s" s="2">
         <v>641</v>
       </c>
       <c r="M97" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="N97" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="N97" t="s" s="2">
+      <c r="O97" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>82</v>
       </c>
@@ -14150,7 +14136,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14162,7 +14148,7 @@
         <v>82</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>105</v>
+        <v>644</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>82</v>
@@ -14171,10 +14157,10 @@
         <v>82</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14183,12 +14169,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14199,32 +14185,28 @@
         <v>80</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>580</v>
+        <v>107</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>646</v>
+        <v>108</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>646</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>647</v>
-      </c>
-      <c r="O98" t="s" s="2">
-        <v>648</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14272,19 +14254,19 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>645</v>
+        <v>110</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>649</v>
+        <v>82</v>
       </c>
       <c r="AK98" t="s" s="2">
         <v>82</v>
@@ -14293,10 +14275,10 @@
         <v>82</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>650</v>
+        <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>651</v>
+        <v>111</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14307,21 +14289,21 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>82</v>
+        <v>113</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>82</v>
@@ -14333,15 +14315,17 @@
         <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N99" s="2"/>
+        <v>116</v>
+      </c>
+      <c r="N99" t="s" s="2">
+        <v>117</v>
+      </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
@@ -14390,19 +14374,19 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ99" t="s" s="2">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="AK99" t="s" s="2">
         <v>82</v>
@@ -14425,14 +14409,14 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
-        <v>113</v>
+        <v>586</v>
       </c>
       <c r="E100" s="2"/>
       <c r="F100" t="s" s="2">
@@ -14445,24 +14429,26 @@
         <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="K100" t="s" s="2">
         <v>114</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>115</v>
+        <v>587</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>116</v>
+        <v>588</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="O100" s="2"/>
+      <c r="O100" t="s" s="2">
+        <v>214</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14510,7 +14496,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>121</v>
+        <v>589</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14534,7 +14520,7 @@
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>111</v>
+        <v>196</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14543,47 +14529,47 @@
         <v>82</v>
       </c>
     </row>
-    <row r="101" hidden="true">
+    <row r="101">
       <c r="A101" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>591</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="G101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="H101" t="s" s="2">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I101" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
         <v>94</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>114</v>
+        <v>256</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>592</v>
+        <v>651</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>593</v>
+        <v>652</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>117</v>
+        <v>653</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>219</v>
+        <v>654</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>82</v>
@@ -14608,13 +14594,13 @@
         <v>82</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>82</v>
+        <v>155</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>82</v>
+        <v>345</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>82</v>
+        <v>346</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>82</v>
@@ -14632,34 +14618,34 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="AG101" t="s" s="2">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="AH101" t="s" s="2">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="AI101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="AK101" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>82</v>
+        <v>655</v>
       </c>
       <c r="AM101" t="s" s="2">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>196</v>
+        <v>350</v>
       </c>
       <c r="AO101" t="s" s="2">
-        <v>82</v>
+        <v>351</v>
       </c>
       <c r="AP101" t="s" s="2">
         <v>82</v>
@@ -14667,10 +14653,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14678,7 +14664,7 @@
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>93</v>
@@ -14693,19 +14679,19 @@
         <v>94</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>261</v>
+        <v>657</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>659</v>
+        <v>436</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>82</v>
@@ -14733,10 +14719,10 @@
         <v>155</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>350</v>
+        <v>661</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>351</v>
+        <v>662</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14754,16 +14740,16 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>93</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>82</v>
+        <v>663</v>
       </c>
       <c r="AJ102" t="s" s="2">
         <v>105</v>
@@ -14772,27 +14758,27 @@
         <v>82</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AM102" t="s" s="2">
-        <v>354</v>
+        <v>441</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>355</v>
+        <v>442</v>
       </c>
       <c r="AO102" t="s" s="2">
-        <v>356</v>
+        <v>82</v>
       </c>
       <c r="AP102" t="s" s="2">
-        <v>82</v>
+        <v>443</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14812,22 +14798,22 @@
         <v>82</v>
       </c>
       <c r="J103" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>662</v>
+        <v>256</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>441</v>
+        <v>503</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
@@ -14855,10 +14841,10 @@
         <v>155</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>666</v>
+        <v>504</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>667</v>
+        <v>505</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14876,7 +14862,7 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
@@ -14885,7 +14871,7 @@
         <v>93</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>105</v>
@@ -14894,22 +14880,22 @@
         <v>82</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>669</v>
+        <v>82</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>446</v>
+        <v>196</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>507</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP103" t="s" s="2">
-        <v>448</v>
+        <v>82</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>670</v>
       </c>
@@ -14918,17 +14904,17 @@
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>82</v>
+        <v>520</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="I104" t="s" s="2">
         <v>82</v>
@@ -14937,19 +14923,19 @@
         <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>671</v>
+        <v>521</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>672</v>
+        <v>522</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>673</v>
+        <v>523</v>
       </c>
       <c r="O104" t="s" s="2">
-        <v>508</v>
+        <v>524</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
@@ -14977,10 +14963,10 @@
         <v>155</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>509</v>
+        <v>671</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>510</v>
+        <v>525</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -15004,10 +14990,10 @@
         <v>80</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="AI104" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="AJ104" t="s" s="2">
         <v>105</v>
@@ -15016,31 +15002,31 @@
         <v>82</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>526</v>
       </c>
       <c r="AM104" t="s" s="2">
-        <v>196</v>
+        <v>527</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>512</v>
+        <v>528</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP104" t="s" s="2">
-        <v>82</v>
+        <v>529</v>
       </c>
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>525</v>
+        <v>82</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -15059,19 +15045,19 @@
         <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>261</v>
+        <v>83</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>526</v>
+        <v>673</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>527</v>
+        <v>674</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>528</v>
+        <v>578</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>529</v>
+        <v>579</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
@@ -15096,13 +15082,13 @@
         <v>82</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>155</v>
+        <v>82</v>
       </c>
       <c r="Y105" t="s" s="2">
-        <v>676</v>
+        <v>82</v>
       </c>
       <c r="Z105" t="s" s="2">
-        <v>530</v>
+        <v>82</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>82</v>
@@ -15120,7 +15106,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -15138,145 +15124,23 @@
         <v>82</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>531</v>
+        <v>82</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>532</v>
+        <v>581</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>533</v>
+        <v>582</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AP105" t="s" s="2">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>678</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>679</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="O106" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="P106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AP106" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP106">
+  <autoFilter ref="A1:AP105">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15286,7 +15150,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI105">
+  <conditionalFormatting sqref="A2:AI104">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.0</t>
+    <t>3.1.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T14:02:34+00:00</t>
+    <t>2026-01-30T09:35:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T09:35:57+00:00</t>
+    <t>2026-01-30T10:15:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.1.1</t>
+    <t>3.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:15:26+00:00</t>
+    <t>2026-02-02T08:09:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:09:27+00:00</t>
+    <t>2026-02-02T08:10:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T08:10:43+00:00</t>
+    <t>2026-02-02T09:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.2.0-ballot</t>
+    <t>3.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:29:40+00:00</t>
+    <t>2026-02-18T12:52:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-18T12:52:41+00:00</t>
+    <t>2026-02-23T17:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>FRANCE</t>
+    <t>France</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:17:29+00:00</t>
+    <t>2026-03-18T17:41:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:41:07+00:00</t>
+    <t>2026-03-31T09:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:00:47+00:00</t>
+    <t>2026-05-06T11:42:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T11:42:59+00:00</t>
+    <t>2026-05-07T07:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:18:48+00:00</t>
+    <t>2026-05-07T07:24:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T07:24:38+00:00</t>
+    <t>2026-06-09T08:46:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
+++ b/main/ig/StructureDefinition-mesures-fr-observation-body-weight.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T08:46:34+00:00</t>
+    <t>2026-06-26T10:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
